--- a/public/data/virulence/campylobacter (1) 2.xlsx
+++ b/public/data/virulence/campylobacter (1) 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hawulethundlovu/Documents/Work/gene_Visualizations/public/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hawulethundlovu/Documents/Work/Salmonella/public/data/virulence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1C1B2F-C5CB-5841-9309-1BDE4E5BCAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE6E5E4-F86D-D544-A7DB-2C42AA768EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{6498390D-C76C-7347-B667-1AEAAB3E8E14}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="202">
   <si>
     <t>Gene Name</t>
   </si>
@@ -829,12 +829,27 @@
   <si>
     <t>from export machinery to move Vi polysaccharide to surface</t>
   </si>
+  <si>
+    <t>avian↑ (early),  bovine↑ (transient), humans ↑↑</t>
+  </si>
+  <si>
+    <t>avian↑ ,  bovine↑ (early), humans ↑↑</t>
+  </si>
+  <si>
+    <t>avian↑ (moderate),  bovine↑↑, humans ↑</t>
+  </si>
+  <si>
+    <t>humans</t>
+  </si>
+  <si>
+    <t>Host 2.0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -957,13 +972,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF9C5700"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1007,9 +1015,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1031,7 +1039,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1368,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41EDA9A-D777-8341-A704-D29AB4C46BFC}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.33203125" customWidth="1"/>
@@ -1385,9 +1394,10 @@
     <col min="14" max="14" width="37.1640625" customWidth="1"/>
     <col min="15" max="15" width="35" customWidth="1"/>
     <col min="16" max="16" width="255.6640625" customWidth="1"/>
+    <col min="17" max="17" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1436,8 +1446,11 @@
       <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q1" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -1487,8 +1500,11 @@
       <c r="P2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="Q2" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>24</v>
       </c>
@@ -1538,8 +1554,11 @@
       <c r="P3" s="13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q3" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
@@ -1589,8 +1608,11 @@
       <c r="P4" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q4" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>40</v>
       </c>
@@ -1640,8 +1662,11 @@
       <c r="P5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
@@ -1691,8 +1716,11 @@
       <c r="P6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>45</v>
       </c>
@@ -1741,8 +1769,11 @@
       <c r="P7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.35">
+      <c r="Q7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="21" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>51</v>
       </c>
@@ -1792,8 +1823,11 @@
       <c r="P8" s="13" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>51</v>
       </c>
@@ -1843,8 +1877,11 @@
       <c r="P9" s="13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="22" x14ac:dyDescent="0.4">
+      <c r="Q9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="22" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>68</v>
       </c>
@@ -1894,8 +1931,11 @@
       <c r="P10" s="13" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="20" x14ac:dyDescent="0.35">
+      <c r="Q10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="20" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>74</v>
       </c>
@@ -1945,8 +1985,11 @@
       <c r="P11" s="13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q11" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>82</v>
       </c>
@@ -1996,8 +2039,11 @@
       <c r="P12" s="13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q12" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>83</v>
       </c>
@@ -2047,8 +2093,11 @@
       <c r="P13" s="13" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q13" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>84</v>
       </c>
@@ -2098,8 +2147,11 @@
       <c r="P14" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q14" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>11</v>
       </c>
@@ -2148,8 +2200,11 @@
       <c r="P15" s="13" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q15" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>109</v>
       </c>
@@ -2198,8 +2253,11 @@
       <c r="P16" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q16" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>115</v>
       </c>
@@ -2248,8 +2306,11 @@
       <c r="P17" s="13" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q17" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>124</v>
       </c>
@@ -2298,8 +2359,11 @@
       <c r="P18" s="13" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q18" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>131</v>
       </c>
@@ -2333,7 +2397,9 @@
       <c r="K19" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="19"/>
+      <c r="L19" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M19" t="s">
         <v>137</v>
       </c>
@@ -2346,8 +2412,11 @@
       <c r="P19" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -2381,7 +2450,9 @@
       <c r="K20" t="s">
         <v>33</v>
       </c>
-      <c r="L20" s="19"/>
+      <c r="L20" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M20" t="s">
         <v>143</v>
       </c>
@@ -2394,8 +2465,11 @@
       <c r="P20" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q20" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>145</v>
       </c>
@@ -2429,7 +2503,9 @@
       <c r="K21" t="s">
         <v>33</v>
       </c>
-      <c r="L21" s="19"/>
+      <c r="L21" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M21" t="s">
         <v>149</v>
       </c>
@@ -2442,8 +2518,11 @@
       <c r="P21" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q21" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>151</v>
       </c>
@@ -2477,7 +2556,9 @@
       <c r="K22" t="s">
         <v>33</v>
       </c>
-      <c r="L22" s="19"/>
+      <c r="L22" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M22" t="s">
         <v>152</v>
       </c>
@@ -2490,8 +2571,11 @@
       <c r="P22" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q22" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>155</v>
       </c>
@@ -2522,7 +2606,9 @@
       <c r="K23" t="s">
         <v>33</v>
       </c>
-      <c r="L23" s="19"/>
+      <c r="L23" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M23" t="s">
         <v>152</v>
       </c>
@@ -2535,8 +2621,11 @@
       <c r="P23" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q23" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>158</v>
       </c>
@@ -2570,7 +2659,9 @@
       <c r="K24" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="19"/>
+      <c r="L24" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M24" t="s">
         <v>152</v>
       </c>
@@ -2583,8 +2674,11 @@
       <c r="P24" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q24" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>161</v>
       </c>
@@ -2618,7 +2712,9 @@
       <c r="K25" t="s">
         <v>167</v>
       </c>
-      <c r="L25" s="19"/>
+      <c r="L25" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M25" t="s">
         <v>168</v>
       </c>
@@ -2631,8 +2727,11 @@
       <c r="P25" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q25" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>171</v>
       </c>
@@ -2666,7 +2765,9 @@
       <c r="K26" t="s">
         <v>167</v>
       </c>
-      <c r="L26" s="19"/>
+      <c r="L26" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M26" t="s">
         <v>152</v>
       </c>
@@ -2679,8 +2780,11 @@
       <c r="P26" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q26" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>174</v>
       </c>
@@ -2714,7 +2818,9 @@
       <c r="K27" t="s">
         <v>176</v>
       </c>
-      <c r="L27" s="19"/>
+      <c r="L27" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M27" t="s">
         <v>152</v>
       </c>
@@ -2727,8 +2833,11 @@
       <c r="P27" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q27" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>178</v>
       </c>
@@ -2762,7 +2871,9 @@
       <c r="K28" t="s">
         <v>180</v>
       </c>
-      <c r="L28" s="19"/>
+      <c r="L28" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M28" t="s">
         <v>152</v>
       </c>
@@ -2775,8 +2886,11 @@
       <c r="P28" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q28" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>182</v>
       </c>
@@ -2810,7 +2924,9 @@
       <c r="K29" t="s">
         <v>183</v>
       </c>
-      <c r="L29" s="19"/>
+      <c r="L29" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="M29" t="s">
         <v>152</v>
       </c>
@@ -2823,8 +2939,11 @@
       <c r="P29" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q29" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>185</v>
       </c>
@@ -2858,7 +2977,9 @@
       <c r="K30" t="s">
         <v>187</v>
       </c>
-      <c r="L30" s="19"/>
+      <c r="L30" s="20" t="s">
+        <v>200</v>
+      </c>
       <c r="M30" t="s">
         <v>152</v>
       </c>
@@ -2871,8 +2992,11 @@
       <c r="P30" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q30" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>189</v>
       </c>
@@ -2903,7 +3027,9 @@
       <c r="K31" t="s">
         <v>191</v>
       </c>
-      <c r="L31" s="19"/>
+      <c r="L31" s="20" t="s">
+        <v>200</v>
+      </c>
       <c r="M31" t="s">
         <v>152</v>
       </c>
@@ -2916,8 +3042,11 @@
       <c r="P31" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="19" x14ac:dyDescent="0.35">
+      <c r="Q31" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="19" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>193</v>
       </c>
@@ -2951,7 +3080,9 @@
       <c r="K32" t="s">
         <v>195</v>
       </c>
-      <c r="L32" s="19"/>
+      <c r="L32" s="20" t="s">
+        <v>200</v>
+      </c>
       <c r="M32" t="s">
         <v>152</v>
       </c>
@@ -2963,6 +3094,9 @@
       </c>
       <c r="P32" t="s">
         <v>196</v>
+      </c>
+      <c r="Q32" s="19" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/virulence/campylobacter (1) 2.xlsx
+++ b/public/data/virulence/campylobacter (1) 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hawulethundlovu/Documents/Work/Salmonella/public/data/virulence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE6E5E4-F86D-D544-A7DB-2C42AA768EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EC109F-2256-424F-A3E3-083DAA45016D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{6498390D-C76C-7347-B667-1AEAAB3E8E14}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="248">
   <si>
     <t>Gene Name</t>
   </si>
@@ -844,12 +844,150 @@
   <si>
     <t>Host 2.0</t>
   </si>
+  <si>
+    <t>motA</t>
+  </si>
+  <si>
+    <t>E. coli</t>
+  </si>
+  <si>
+    <t>NC_000913.3</t>
+  </si>
+  <si>
+    <t>1976252..1977139, complement</t>
+  </si>
+  <si>
+    <t>motility protein A</t>
+  </si>
+  <si>
+    <t>key component of the flagellar motor. Together with MotB, it forms a proton channel in the inner membrane that converts the proton motive force into rotation of the flagellum.</t>
+  </si>
+  <si>
+    <t>motB</t>
+  </si>
+  <si>
+    <t>1975329..1976255, complement</t>
+  </si>
+  <si>
+    <t>motility protein B</t>
+  </si>
+  <si>
+    <t>encodes the stator anchor of the flagellar motor. It works with MotA to form a proton channel and is anchored to the peptidoglycan layer, stabilizing the motor.</t>
+  </si>
+  <si>
+    <t>fimA</t>
+  </si>
+  <si>
+    <t>4543115..4543663</t>
+  </si>
+  <si>
+    <t>type 1 fimbriae major subunit</t>
+  </si>
+  <si>
+    <t>encodes the major structural subunit of type 1 fimbriae (pili) and forms the bulk of type 1 fimbriae, which mediate adhesion to host cells.</t>
+  </si>
+  <si>
+    <t>fimB</t>
+  </si>
+  <si>
+    <t>4540957..4541559</t>
+  </si>
+  <si>
+    <t>type 1 fimbriae regulatory protein FimB</t>
+  </si>
+  <si>
+    <t>FimB, along with FimE, is a recombinase in Escherichia coli which catalyzes the site-specific recombination required for inversion of a 314-bp invertible DNA element, the fim switch (fimS), to control transcription of the type I fimbrial structural genes--a process known as phase-variation switching. fimS contains the promoter for expression of the fimbrial structural genes.</t>
+  </si>
+  <si>
+    <t>fimC</t>
+  </si>
+  <si>
+    <t>4544304..4545029</t>
+  </si>
+  <si>
+    <t>type 1 fimbriae periplasmic chaperone</t>
+  </si>
+  <si>
+    <t>FimC is a member of the periplasmic chaperone family which functions in the chaperone-usher pathway and is indispensable in the biogenesis of the type 1 pilus fiber of Escherichia coli.</t>
+  </si>
+  <si>
+    <t>fimD</t>
+  </si>
+  <si>
+    <t>4545096..4547732</t>
+  </si>
+  <si>
+    <t>type I fimbriae usher protein</t>
+  </si>
+  <si>
+    <t>FimD is the usher protein of the type 1 fimbrial assembly system in Escherichia coli. It forms an outer membrane pore that facilitates the assembly and export of fimbrial subunits (including FimA and the adhesin FimH) to the bacterial surface.</t>
+  </si>
+  <si>
+    <t>fimE</t>
+  </si>
+  <si>
+    <t>4542037..4542633</t>
+  </si>
+  <si>
+    <t>regulator for fimA</t>
+  </si>
+  <si>
+    <t>FimE forms a transient covalent Tyr linkage to DNA. FimE, along with FimB, is a recombinase in Escherichia coli which catalyzes the site-specific recombination.</t>
+  </si>
+  <si>
+    <t>fimH</t>
+  </si>
+  <si>
+    <t>4548808..4549710</t>
+  </si>
+  <si>
+    <t>type 1 fimbriae D-mannose specific adhesin</t>
+  </si>
+  <si>
+    <t>FimF is a minor pilus tip-adaptor protein involved in the assembly of type 1 fimbriae in Escherichia coli. It acts as a connector between the major pilus shaft (FimA) and the tip adhesin complex (FimH).</t>
+  </si>
+  <si>
+    <t>eae</t>
+  </si>
+  <si>
+    <t>4596583..4599387, complement</t>
+  </si>
+  <si>
+    <t>T3SS intimin</t>
+  </si>
+  <si>
+    <t>he eae gene encodes intimin, a key outer membrane adhesin found in pathogenic Escherichia coli, especially enteropathogenic (EPEC) and enterohemorrhagic (EHEC) strains. Intimin is located on the locus of enterocyte effacement (LEE) pathogenicity island.</t>
+  </si>
+  <si>
+    <t>espA</t>
+  </si>
+  <si>
+    <t>4593264..4593842, complement</t>
+  </si>
+  <si>
+    <t>T3SS translocator EspA</t>
+  </si>
+  <si>
+    <t>The espA gene encodes the EspA protein, a key component of the Type III secretion system (T3SS) in pathogenic Escherichia coli, particularly enteropathogenic (EPEC) and enterohemorrhagic (EHEC) strains. EspA forms a long filamentous needle-like structure that bridges the bacterium and the host cell.</t>
+  </si>
+  <si>
+    <t>fliC</t>
+  </si>
+  <si>
+    <t>2002110..2003606, complement</t>
+  </si>
+  <si>
+    <t>flagellar filament structural protein</t>
+  </si>
+  <si>
+    <t>FliC, or flagellin, is the basic subunit that polymerizes to form the rigid flagellar filament of Escherichia coli.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -977,6 +1115,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1017,7 +1171,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1041,6 +1195,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1377,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41EDA9A-D777-8341-A704-D29AB4C46BFC}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.33203125" customWidth="1"/>
@@ -3097,6 +3254,391 @@
       </c>
       <c r="Q32" s="19" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E33" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>152</v>
+      </c>
+      <c r="I33" t="s">
+        <v>206</v>
+      </c>
+      <c r="J33" t="s">
+        <v>152</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>208</v>
+      </c>
+      <c r="B34" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I34" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" t="s">
+        <v>152</v>
+      </c>
+      <c r="K34" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" t="s">
+        <v>213</v>
+      </c>
+      <c r="E35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>152</v>
+      </c>
+      <c r="I35" t="s">
+        <v>214</v>
+      </c>
+      <c r="J35" t="s">
+        <v>152</v>
+      </c>
+      <c r="K35" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E36" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>152</v>
+      </c>
+      <c r="I36" t="s">
+        <v>218</v>
+      </c>
+      <c r="J36" t="s">
+        <v>152</v>
+      </c>
+      <c r="K36" s="22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="J37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>152</v>
+      </c>
+      <c r="I38" t="s">
+        <v>226</v>
+      </c>
+      <c r="J38" t="s">
+        <v>152</v>
+      </c>
+      <c r="K38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="E39" t="s">
+        <v>152</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>152</v>
+      </c>
+      <c r="I39" t="s">
+        <v>230</v>
+      </c>
+      <c r="J39" t="s">
+        <v>152</v>
+      </c>
+      <c r="K39" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>232</v>
+      </c>
+      <c r="B40" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>152</v>
+      </c>
+      <c r="I40" t="s">
+        <v>234</v>
+      </c>
+      <c r="J40" t="s">
+        <v>152</v>
+      </c>
+      <c r="K40" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" t="s">
+        <v>152</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>152</v>
+      </c>
+      <c r="I41" t="s">
+        <v>238</v>
+      </c>
+      <c r="J41" t="s">
+        <v>152</v>
+      </c>
+      <c r="K41" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="J42" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>152</v>
+      </c>
+      <c r="I43" t="s">
+        <v>246</v>
+      </c>
+      <c r="J43" t="s">
+        <v>152</v>
+      </c>
+      <c r="K43" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
